--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Automation_Product\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888E3D2F-9D18-492E-84C9-79D8EBA94FCE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4BB2946-701B-4261-B53A-894B5C2294FF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="11" activeTab="13" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="10" activeTab="13" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -153,9 +153,6 @@
     <t>fieldInternalOrganization__c</t>
   </si>
   <si>
-    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
-  </si>
-  <si>
     <t>Program__c</t>
   </si>
   <si>
@@ -165,9 +162,6 @@
     <t>ExternalOrganization__c</t>
   </si>
   <si>
-    <t>Test Automation Organization</t>
-  </si>
-  <si>
     <t>IsMatchRequired__c</t>
   </si>
   <si>
@@ -283,13 +277,19 @@
   </si>
   <si>
     <t>Terms and Conditions Change</t>
+  </si>
+  <si>
+    <t>Southside Community Criminal Justice Board</t>
+  </si>
+  <si>
+    <t>Basic Field Grant Office</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,6 +309,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -327,10 +342,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -342,8 +358,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -657,13 +678,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -674,7 +695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -685,7 +706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -696,7 +717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -716,13 +737,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,67 +754,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -807,13 +828,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -824,67 +845,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>58</v>
       </c>
-      <c r="C2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>62</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -898,13 +919,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,7 +936,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -923,10 +944,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -937,7 +958,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -956,13 +977,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -973,34 +994,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3">
         <v>650</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>1000</v>
@@ -1015,13 +1036,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.6328125" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,7 +1053,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1040,10 +1061,10 @@
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1054,7 +1075,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1073,14 +1094,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1091,7 +1112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1102,7 +1123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1113,7 +1134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1124,7 +1145,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1135,7 +1156,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1146,7 +1167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1157,7 +1178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1168,7 +1189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1179,7 +1200,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1198,13 +1219,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1236,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1226,7 +1247,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1237,7 +1258,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1256,13 +1277,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1273,7 +1294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1284,15 +1305,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1304,13 +1325,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1321,26 +1342,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
         <v>70</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
         <v>71</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1351,13 +1372,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1368,7 +1389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1379,7 +1400,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1390,7 +1411,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1410,13 +1431,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1448,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1435,10 +1456,10 @@
         <v>28</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +1470,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1460,7 +1481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1492,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1482,54 +1503,58 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
+      <c r="C9" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C9" r:id="rId1" tooltip="Basic Field Grant Office" display="https://test7-internal--lsc--c.cs92.visual.force.com/0013F00000UJsYpQAL" xr:uid="{BB5ED863-80D3-4613-8AAD-CE782A1AD3BB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1540,125 +1565,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1669,13 +1694,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1686,23 +1711,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>54</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" t="s">
-        <v>57</v>
       </c>
       <c r="C3">
         <v>3650</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98AA166-91E0-4F58-92C0-14DCADB4A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79EDE2-EB4E-48BF-B7D0-081B5590DD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="13" activeTab="14" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="99">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -355,6 +355,12 @@
   </si>
   <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>NewBudgetPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>BudgetPeriodComments__c</t>
   </si>
 </sst>
 </file>
@@ -760,13 +766,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,7 +783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -788,7 +794,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -799,7 +805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -819,14 +825,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,7 +843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -848,7 +854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -859,7 +865,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -870,7 +876,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -881,7 +887,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -892,7 +898,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -903,7 +909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -914,7 +920,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -925,7 +931,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -944,13 +950,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -961,7 +967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -972,7 +978,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -983,7 +989,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1002,13 +1008,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1030,7 +1036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1041,7 +1047,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1061,13 +1067,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,7 +1084,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1111,7 +1117,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1130,12 +1136,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,7 +1152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1157,7 +1163,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1168,7 +1174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1179,7 +1185,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1190,7 +1196,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1209,13 +1215,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1226,23 +1232,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>81</v>
+      <c r="B2" t="s">
+        <v>97</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
         <v>52</v>
@@ -1257,14 +1263,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,7 +1281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1286,7 +1292,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1305,13 +1311,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,7 +1328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1333,7 +1339,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1344,7 +1350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1363,13 +1369,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1391,7 +1397,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1410,13 +1416,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1438,7 +1444,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1469,13 +1475,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1486,7 +1492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1497,7 +1503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1508,7 +1514,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1538,13 +1544,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1555,7 +1561,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1566,7 +1572,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1577,7 +1583,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1599,7 +1605,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1610,7 +1616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1621,7 +1627,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1632,7 +1638,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1651,13 +1657,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1668,7 +1674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1679,7 +1685,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1690,7 +1696,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1701,7 +1707,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1712,7 +1718,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1723,7 +1729,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1734,7 +1740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1745,7 +1751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1756,7 +1762,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1767,7 +1773,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1778,7 +1784,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1797,13 +1803,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1814,7 +1820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1825,7 +1831,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1844,13 +1850,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1861,7 +1867,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1872,7 +1878,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1883,7 +1889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1894,7 +1900,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1905,7 +1911,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1916,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1935,13 +1941,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1952,7 +1958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1963,7 +1969,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1974,7 +1980,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1985,7 +1991,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1996,7 +2002,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2007,7 +2013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2026,13 +2032,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2043,7 +2049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2054,7 +2060,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2065,7 +2071,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2084,13 +2090,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2101,7 +2107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2112,7 +2118,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2134,7 +2140,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2145,7 +2151,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2156,7 +2162,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2167,7 +2173,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2187,13 +2193,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2204,7 +2210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2215,7 +2221,7 @@
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2226,7 +2232,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2237,7 +2243,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2248,7 +2254,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2259,7 +2265,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2270,7 +2276,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2289,13 +2295,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2306,7 +2312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2317,7 +2323,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2328,7 +2334,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2339,7 +2345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2358,13 +2364,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2375,7 +2381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2386,7 +2392,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2397,7 +2403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2416,13 +2422,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2433,7 +2439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2444,7 +2450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2455,7 +2461,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2466,7 +2472,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2477,7 +2483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2496,13 +2502,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2513,7 +2519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2524,7 +2530,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2535,7 +2541,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2546,7 +2552,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2557,7 +2563,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2587,14 +2593,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2605,7 +2611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2616,7 +2622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2627,7 +2633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2647,14 +2653,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2665,7 +2671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2676,7 +2682,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2687,7 +2693,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2707,13 +2713,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2724,7 +2730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2735,7 +2741,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2746,7 +2752,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2766,13 +2772,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2783,7 +2789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2794,7 +2800,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2805,7 +2811,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2816,7 +2822,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2835,13 +2841,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2863,7 +2869,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2874,7 +2880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2893,14 +2899,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2911,7 +2917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2922,7 +2928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2933,7 +2939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2944,7 +2950,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2955,7 +2961,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2966,7 +2972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2977,7 +2983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2988,7 +2994,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2999,7 +3005,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3010,7 +3016,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backward\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98AA166-91E0-4F58-92C0-14DCADB4A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313431C4-C605-4582-B9AB-38F56A9D928F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -96,30 +96,18 @@
     <t>Automation Overall Impact</t>
   </si>
   <si>
-    <t>ScopeofWorkChangeDescription__c</t>
-  </si>
-  <si>
     <t>Automation Justification for Scope of Work Change</t>
   </si>
   <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>Addressline1__c</t>
-  </si>
-  <si>
     <t>Automation Address 1</t>
   </si>
   <si>
-    <t>Addressline2__c</t>
-  </si>
-  <si>
     <t>Automation Address 2</t>
   </si>
   <si>
-    <t>City__c</t>
-  </si>
-  <si>
     <t>Automation City</t>
   </si>
   <si>
@@ -129,9 +117,6 @@
     <t>Zip4__c</t>
   </si>
   <si>
-    <t>Congressionaldistrict__c</t>
-  </si>
-  <si>
     <t>Budget Period Change</t>
   </si>
   <si>
@@ -355,13 +340,22 @@
   </si>
   <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>fieldZip4__c</t>
+  </si>
+  <si>
+    <t>fieldCongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>fieldGrantAwardDescription__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -406,6 +400,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -427,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -445,6 +445,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -760,13 +761,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,18 +778,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -799,7 +800,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -819,14 +820,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,103 +838,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
       </c>
       <c r="C8">
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -944,13 +945,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -961,18 +962,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -983,7 +984,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1002,13 +1003,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,34 +1020,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1061,13 +1062,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,45 +1079,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1130,12 +1131,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,56 +1147,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1209,13 +1210,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1226,26 +1227,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1257,14 +1258,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,26 +1276,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1305,13 +1306,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,34 +1323,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1363,13 +1364,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1380,26 +1381,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1411,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,18 +1428,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +1450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1469,13 +1470,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1486,29 +1487,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1519,7 +1520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1538,13 +1539,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1555,92 +1556,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C9" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1651,13 +1652,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1668,125 +1669,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="C11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1797,13 +1798,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1814,23 +1815,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1844,13 +1845,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1861,67 +1862,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1935,13 +1936,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1952,67 +1953,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C4" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -2026,13 +2027,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2043,34 +2044,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>77</v>
-      </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2084,13 +2085,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2101,78 +2102,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2187,13 +2188,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2204,78 +2205,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2289,13 +2290,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2306,29 +2307,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2339,7 +2340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2358,13 +2359,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2375,18 +2376,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2397,7 +2398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2416,13 +2417,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2433,40 +2434,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2477,7 +2478,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2496,13 +2497,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2513,51 +2514,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2587,14 +2588,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2605,34 +2606,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2647,14 +2648,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2665,18 +2666,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2687,7 +2688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2707,13 +2708,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2724,34 +2725,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2766,13 +2767,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2783,45 +2784,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -2835,13 +2836,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2852,34 +2853,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2893,14 +2894,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2911,114 +2912,114 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>73</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
+        <v>11</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>92</v>
       </c>
       <c r="C9">
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>21</v>
+        <v>11</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>93</v>
       </c>
       <c r="C10">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA79EDE2-EB4E-48BF-B7D0-081B5590DD82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EF1143-3A78-4C68-8245-3D3227AECBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="13" activeTab="14" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="104">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -318,9 +318,6 @@
     <t>Carry Forward</t>
   </si>
   <si>
-    <t>fieldInternalAmendmentType__c</t>
-  </si>
-  <si>
     <t>fieldCountry__c</t>
   </si>
   <si>
@@ -361,6 +358,24 @@
   </si>
   <si>
     <t>BudgetPeriodComments__c</t>
+  </si>
+  <si>
+    <t>ProposedBudgetEndDate__c</t>
+  </si>
+  <si>
+    <t>RequestedChangeInBudget__c</t>
+  </si>
+  <si>
+    <t>County__c</t>
+  </si>
+  <si>
+    <t>Country__c</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>RevisedCommitment__c</t>
   </si>
 </sst>
 </file>
@@ -469,9 +484,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -509,7 +524,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -615,7 +630,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -757,7 +772,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -870,7 +885,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -881,7 +896,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -892,7 +907,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -903,7 +918,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -936,10 +951,10 @@
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1252,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1248,7 +1263,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
         <v>52</v>
@@ -2054,7 +2069,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>72</v>
@@ -2065,7 +2080,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2076,7 +2091,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2112,7 +2127,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -2123,7 +2138,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -2134,7 +2149,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -2145,10 +2160,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2156,7 +2171,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2167,10 +2182,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
         <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2178,7 +2193,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2215,7 +2230,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
@@ -2237,7 +2252,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
@@ -2248,10 +2263,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2270,10 +2285,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2281,7 +2296,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2988,10 +3003,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -3021,7 +3036,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4EF1143-3A78-4C68-8245-3D3227AECBFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E822F9-6113-4D97-928B-53B5E933CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="105">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>RevisedCommitment__c</t>
+  </si>
+  <si>
+    <t>CongressionalDistrict__c</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2174,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>123</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E822F9-6113-4D97-928B-53B5E933CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E7C586-B397-4F2A-B331-234D43A4E6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="19" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Construction</t>
   </si>
   <si>
-    <t>fieldInternalOrganization__c</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
@@ -264,9 +261,6 @@
     <t>Automation Execution Award for Amendment Request</t>
   </si>
   <si>
-    <t>fieldBudgetPeriodComments__c</t>
-  </si>
-  <si>
     <t>Financials</t>
   </si>
   <si>
@@ -285,72 +279,27 @@
     <t>Periodic Renewal</t>
   </si>
   <si>
-    <t>fieldRequestedChangeInBudget__c</t>
-  </si>
-  <si>
     <t>Terms and Conditions Change</t>
   </si>
   <si>
     <t>Budget Redirection</t>
   </si>
   <si>
-    <t>fieldSubAmendmentType__c</t>
-  </si>
-  <si>
-    <t>fieldPurposeRTA__c</t>
-  </si>
-  <si>
-    <t>fieldImpact__c</t>
-  </si>
-  <si>
-    <t>fieldScopeofWorkChangeDescription__c</t>
-  </si>
-  <si>
-    <t>fieldCongressionaldistrict__c</t>
-  </si>
-  <si>
-    <t>fieldNewBudgetPeriodEndDate__c</t>
-  </si>
-  <si>
     <t>Key Personnel Change</t>
   </si>
   <si>
     <t>Carry Forward</t>
   </si>
   <si>
-    <t>fieldCountry__c</t>
-  </si>
-  <si>
-    <t>fieldCounty__c</t>
-  </si>
-  <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
     <t>LA</t>
   </si>
   <si>
     <t>VA</t>
   </si>
   <si>
-    <t>fieldProposedBudgetEndDate__c</t>
-  </si>
-  <si>
-    <t>fieldCity__c</t>
-  </si>
-  <si>
     <t>US</t>
   </si>
   <si>
-    <t>fieldAddressline1__c</t>
-  </si>
-  <si>
-    <t>fieldAddressline2__c</t>
-  </si>
-  <si>
-    <t>fieldRevisedCommitment__c</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
@@ -379,13 +328,19 @@
   </si>
   <si>
     <t>CongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>SubAmendmentType__c</t>
+  </si>
+  <si>
+    <t>InternalOrganization__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,12 +368,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="5"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF202124"/>
       <name val="Consolas"/>
@@ -427,6 +376,38 @@
     <font>
       <sz val="9"/>
       <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF202124"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -451,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -468,7 +449,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,13 +776,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -812,7 +804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -823,7 +815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -843,121 +835,121 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="12" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
+      <c r="B2" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>78</v>
+      <c r="B3" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>92</v>
+      <c r="B4" s="15" t="s">
+        <v>13</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>93</v>
+      <c r="B5" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>90</v>
+      <c r="B6" s="15" t="s">
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>85</v>
+      <c r="B7" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="12" t="s">
         <v>20</v>
       </c>
       <c r="C8">
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>80</v>
+      <c r="B9" s="15" t="s">
+        <v>21</v>
       </c>
       <c r="C9">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="15" t="s">
         <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -968,13 +960,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -996,7 +988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1007,7 +999,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1026,51 +1018,51 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
+      <c r="B3" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
+      <c r="B4" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1085,62 +1077,62 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>76</v>
+      <c r="B3" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>77</v>
+      <c r="B4" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>78</v>
+      <c r="B5" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1154,72 +1146,73 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>76</v>
+      <c r="B3" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>76</v>
+      <c r="B4" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>77</v>
+      <c r="B5" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>78</v>
+      <c r="B6" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1233,13 +1226,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1250,26 +1243,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1281,44 +1274,44 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40" style="12" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>81</v>
+      <c r="B2" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>66</v>
+      <c r="B3" s="14" t="s">
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1329,51 +1322,51 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="12" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
+      <c r="B3" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
+      <c r="B4" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1387,13 +1380,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1404,26 +1397,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1434,13 +1427,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1451,7 +1444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1462,7 +1455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1473,7 +1466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1493,13 +1486,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1521,7 +1514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1532,7 +1525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1543,7 +1536,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1562,13 +1555,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1587,10 +1580,10 @@
         <v>25</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1601,7 +1594,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1612,7 +1605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1623,7 +1616,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1634,37 +1627,37 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1675,13 +1668,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1692,125 +1685,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1821,13 +1814,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1838,23 +1831,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1868,13 +1861,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1885,67 +1878,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>62</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1959,13 +1952,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1976,67 +1969,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>62</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -2050,13 +2043,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2075,10 +2068,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2089,7 +2082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2108,13 +2101,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2125,78 +2118,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>98</v>
+      <c r="B2" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>100</v>
+      <c r="B4" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>101</v>
+      <c r="B5" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>104</v>
+      <c r="B6" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>102</v>
+      <c r="B7" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>103</v>
+      <c r="B8" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2211,13 +2204,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2228,78 +2221,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>89</v>
+      <c r="B2" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>85</v>
+      <c r="B4" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>80</v>
+      <c r="B6" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>94</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2313,13 +2306,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2330,7 +2323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2341,7 +2334,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2349,10 +2342,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2363,7 +2356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2382,13 +2375,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2399,7 +2392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2407,10 +2400,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2421,7 +2414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2440,13 +2433,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2457,7 +2450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2468,7 +2461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2479,7 +2472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2490,7 +2483,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2501,7 +2494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2520,13 +2513,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2537,7 +2530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2548,7 +2541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2559,29 +2552,29 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C4" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C5" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2592,7 +2585,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2611,52 +2604,52 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
+      <c r="B3" s="13" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
+      <c r="B4" s="13" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2671,14 +2664,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2689,7 +2682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2697,10 +2690,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2711,7 +2704,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2731,51 +2724,51 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
+      <c r="B3" s="14" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
+      <c r="B4" s="14" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2790,13 +2783,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2807,45 +2800,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -2859,51 +2852,51 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="12" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>76</v>
+      <c r="B2" s="11" t="s">
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>77</v>
+      <c r="B3" s="11" t="s">
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
+      <c r="B4" s="11" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2917,14 +2910,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2935,7 +2928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2946,7 +2939,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2957,7 +2950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2968,7 +2961,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2979,7 +2972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2990,7 +2983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3001,18 +2994,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3023,7 +3016,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3034,12 +3027,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>85</v>
+      <c r="B11" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E822F9-6113-4D97-928B-53B5E933CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE23DCDF-F6D8-4BF3-896B-B646C4C12ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="24" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,11 @@
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId24"/>
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId25"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId26"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId27"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId28"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId29"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId30"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId27"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId28"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId29"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId30"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="105">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -2209,6 +2210,96 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7">
+        <v>2000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2310,7 +2401,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2371,64 +2462,6 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -2518,6 +2551,64 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE23DCDF-F6D8-4BF3-896B-B646C4C12ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82DAD7B-78B3-48BA-A746-94866A87C7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="24" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -3097,7 +3097,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
         <v>95</v>
@@ -3130,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82DAD7B-78B3-48BA-A746-94866A87C7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE210754-1F20-43C1-885A-ADC54AE9D328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="24" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE210754-1F20-43C1-885A-ADC54AE9D328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084ACBA3-F300-4004-A905-C06B43894056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="24" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="104">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -128,9 +128,6 @@
   </si>
   <si>
     <t>Zip4__c</t>
-  </si>
-  <si>
-    <t>Congressionaldistrict__c</t>
   </si>
   <si>
     <t>Budget Period Change</t>
@@ -807,7 +804,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -867,7 +864,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -878,7 +875,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
@@ -889,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
@@ -900,7 +897,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -911,7 +908,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
@@ -922,7 +919,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -944,7 +941,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="C9">
         <v>123</v>
@@ -955,10 +952,10 @@
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -991,10 +988,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1049,10 +1046,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1060,7 +1057,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1071,7 +1068,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1108,10 +1105,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1119,7 +1116,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1130,7 +1127,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1141,7 +1138,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1176,10 +1173,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1187,7 +1184,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1198,10 +1195,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1209,7 +1206,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1220,7 +1217,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1256,7 +1253,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1267,10 +1264,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1305,7 +1302,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1316,10 +1313,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1352,10 +1349,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1363,7 +1360,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1374,7 +1371,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1407,24 +1404,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" t="s">
         <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1457,10 +1454,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1516,7 +1513,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1527,10 +1524,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1585,10 +1582,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1596,10 +1593,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1607,7 +1604,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1618,7 +1615,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>3650</v>
@@ -1629,10 +1626,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1640,10 +1637,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -1651,10 +1648,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1662,10 +1659,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1698,10 +1695,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1709,10 +1706,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1720,10 +1717,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1731,10 +1728,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1742,10 +1739,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1753,10 +1750,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -1764,10 +1761,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1775,10 +1772,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -1786,10 +1783,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -1797,10 +1794,10 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -1808,10 +1805,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1844,18 +1841,18 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1891,10 +1888,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
         <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1902,10 +1899,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1913,10 +1910,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
         <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1924,10 +1921,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1935,7 +1932,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1946,7 +1943,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1982,10 +1979,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1993,10 +1990,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2004,10 +2001,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
         <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2015,10 +2012,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2026,7 +2023,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -2037,7 +2034,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -2073,10 +2070,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2131,7 +2128,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -2142,7 +2139,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -2153,10 +2150,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2164,10 +2161,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2175,7 +2172,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2186,10 +2183,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2197,7 +2194,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2233,7 +2230,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -2244,10 +2241,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2255,10 +2252,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2266,7 +2263,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -2277,10 +2274,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -2288,7 +2285,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7">
         <v>2000</v>
@@ -2324,7 +2321,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
@@ -2335,7 +2332,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -2346,10 +2343,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2357,10 +2354,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2368,7 +2365,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2379,10 +2376,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
         <v>86</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2390,7 +2387,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2426,10 +2423,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2437,10 +2434,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2495,7 +2492,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2506,10 +2503,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2517,10 +2514,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2575,10 +2572,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2633,7 +2630,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2644,10 +2641,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2655,10 +2652,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2666,10 +2663,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2725,7 +2722,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2736,7 +2733,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2747,7 +2744,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2785,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2844,10 +2841,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2855,7 +2852,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2866,7 +2863,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2903,10 +2900,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2914,10 +2911,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -2925,7 +2922,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2936,7 +2933,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -2972,10 +2969,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -2983,7 +2980,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2994,7 +2991,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -3097,10 +3094,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -3119,7 +3116,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3130,7 +3127,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E7C586-B397-4F2A-B331-234D43A4E6B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6B467D-1FB2-4A42-9446-24373D0CFF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="19" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -432,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -449,10 +449,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -838,7 +834,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" style="10" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -846,7 +842,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -857,7 +853,7 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
@@ -868,7 +864,7 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
@@ -879,7 +875,7 @@
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
@@ -890,7 +886,7 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
@@ -901,7 +897,7 @@
       <c r="A6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
@@ -912,7 +908,7 @@
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C7" t="s">
@@ -923,7 +919,7 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>20</v>
       </c>
       <c r="C8">
@@ -934,7 +930,7 @@
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="13" t="s">
         <v>21</v>
       </c>
       <c r="C9">
@@ -945,7 +941,7 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>84</v>
       </c>
       <c r="C10" t="s">
@@ -1020,7 +1016,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1028,7 +1024,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1039,7 +1035,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -1050,7 +1046,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -1061,7 +1057,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
@@ -1079,7 +1075,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="36.28515625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="36.28515625" style="10" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1087,7 +1083,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1098,7 +1094,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -1109,7 +1105,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C3" t="s">
@@ -1120,7 +1116,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C4" t="s">
@@ -1131,7 +1127,7 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C5" t="s">
@@ -1148,7 +1144,7 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="33.85546875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" style="10" customWidth="1"/>
     <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1156,7 +1152,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1167,7 +1163,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -1178,7 +1174,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C3" t="s">
@@ -1189,7 +1185,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C4" t="s">
@@ -1200,7 +1196,7 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C5" t="s">
@@ -1211,7 +1207,7 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
@@ -1277,7 +1273,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40" style="12" customWidth="1"/>
+    <col min="2" max="2" width="40" style="10" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1285,7 +1281,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1296,7 +1292,7 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>79</v>
       </c>
       <c r="C2">
@@ -1307,7 +1303,7 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C3" t="s">
@@ -1324,7 +1320,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.5703125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="35.5703125" style="10" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1332,7 +1328,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -1343,7 +1339,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -1354,7 +1350,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -1365,7 +1361,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
@@ -2607,7 +2603,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2615,7 +2611,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2626,7 +2622,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -2637,7 +2633,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -2648,7 +2644,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
@@ -2667,7 +2663,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
     <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2726,7 +2722,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" style="10" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2734,7 +2730,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2745,7 +2741,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="12" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -2756,7 +2752,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -2767,7 +2763,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">
@@ -2854,7 +2850,7 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.42578125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="31.42578125" style="10" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2862,7 +2858,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -2873,7 +2869,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">
@@ -2884,7 +2880,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>5</v>
       </c>
       <c r="C3" t="s">
@@ -2895,7 +2891,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C4" t="s">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E6B467D-1FB2-4A42-9446-24373D0CFF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CA2451-A668-47F2-9822-13F477016156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -2723,7 +2723,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E822F9-6113-4D97-928B-53B5E933CFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6CE629-2B27-4E45-85CF-762E651B2468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="1524" yWindow="2472" windowWidth="17280" windowHeight="8880" firstSheet="25" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="101">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -285,9 +285,6 @@
     <t>Periodic Renewal</t>
   </si>
   <si>
-    <t>fieldRequestedChangeInBudget__c</t>
-  </si>
-  <si>
     <t>Terms and Conditions Change</t>
   </si>
   <si>
@@ -324,18 +321,12 @@
     <t>fieldCounty__c</t>
   </si>
   <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
     <t>LA</t>
   </si>
   <si>
     <t>VA</t>
   </si>
   <si>
-    <t>fieldProposedBudgetEndDate__c</t>
-  </si>
-  <si>
     <t>fieldCity__c</t>
   </si>
   <si>
@@ -346,9 +337,6 @@
   </si>
   <si>
     <t>fieldAddressline2__c</t>
-  </si>
-  <si>
-    <t>fieldRevisedCommitment__c</t>
   </si>
   <si>
     <t>USA</t>
@@ -784,13 +772,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,7 +789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -812,7 +800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -823,7 +811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -843,14 +831,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,73 +849,73 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -938,26 +926,26 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -968,13 +956,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -985,7 +973,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -996,7 +984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1007,7 +995,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1026,13 +1014,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1043,34 +1031,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1085,13 +1073,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1102,45 +1090,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1154,12 +1142,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1170,56 +1158,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1233,13 +1221,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1250,23 +1238,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
         <v>52</v>
@@ -1281,14 +1269,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1299,18 +1287,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1329,13 +1317,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1346,34 +1334,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1387,13 +1375,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1392,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -1415,7 +1403,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1434,13 +1422,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1451,7 +1439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1462,7 +1450,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1473,7 +1461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1493,13 +1481,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1521,7 +1509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1532,7 +1520,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1543,7 +1531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1562,13 +1550,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1590,7 +1578,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1601,7 +1589,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1612,7 +1600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1623,7 +1611,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1634,7 +1622,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1645,7 +1633,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1656,7 +1644,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1675,13 +1663,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1692,7 +1680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1703,7 +1691,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1714,7 +1702,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1725,7 +1713,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1736,7 +1724,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1747,7 +1735,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1758,7 +1746,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1769,7 +1757,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1780,7 +1768,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1791,7 +1779,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1802,7 +1790,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1821,13 +1809,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1838,7 +1826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1849,7 +1837,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>53</v>
       </c>
@@ -1868,13 +1856,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1885,7 +1873,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1896,7 +1884,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1907,7 +1895,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1918,7 +1906,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1929,7 +1917,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1940,7 +1928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1959,13 +1947,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1976,7 +1964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1987,7 +1975,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1998,7 +1986,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2009,7 +1997,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2020,7 +2008,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2031,7 +2019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2050,13 +2038,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2078,7 +2066,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2089,7 +2077,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2108,13 +2096,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2125,78 +2113,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2211,13 +2199,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2228,78 +2216,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2313,13 +2301,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2330,7 +2318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2341,7 +2329,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2349,10 +2337,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2363,7 +2351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2382,13 +2370,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2399,7 +2387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2407,10 +2395,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2421,7 +2409,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2440,13 +2428,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2457,7 +2445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2468,7 +2456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2479,7 +2467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2490,7 +2478,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2501,7 +2489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2520,13 +2508,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2537,7 +2525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2548,7 +2536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2559,7 +2547,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2570,7 +2558,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2578,10 +2566,10 @@
         <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2592,7 +2580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2611,14 +2599,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2629,34 +2617,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2671,14 +2659,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2689,7 +2677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2697,10 +2685,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2711,7 +2699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2731,13 +2719,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2748,34 +2736,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2790,13 +2778,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2807,45 +2795,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -2859,13 +2847,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2876,34 +2864,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2917,14 +2905,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2935,7 +2923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2946,7 +2934,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2957,7 +2945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2968,7 +2956,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2979,7 +2967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2990,7 +2978,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3001,18 +2989,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3023,7 +3011,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3034,12 +3022,12 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D6CE629-2B27-4E45-85CF-762E651B2468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E03F7C9-E210-4E7E-9F06-8E06887498C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1524" yWindow="2472" windowWidth="17280" windowHeight="8880" firstSheet="25" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="24" activeTab="24" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CA2451-A668-47F2-9822-13F477016156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA86150-0AE8-4884-B44A-A1DF8C8853ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -2683,7 +2683,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
         <v>72</v>
@@ -2723,7 +2723,7 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.5703125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="71.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2733,7 +2733,7 @@
       <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>88</v>
       </c>
       <c r="C2" t="s">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,45 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59D6A6BC-3D67-4B6A-A9BB-0A71E8239ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98AA166-91E0-4F58-92C0-14DCADB4A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="90" windowWidth="20370" windowHeight="10920" firstSheet="8" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Scope&amp;BudgetPeriod_Creation" sheetId="25" r:id="rId2"/>
-    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId3"/>
-    <sheet name="Budget_Redirection" sheetId="15" r:id="rId4"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId5"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId6"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId7"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId8"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId9"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId10"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId11"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId12"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId13"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId14"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId15"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId16"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId17"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId18"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId19"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId20"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId21"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId22"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId23"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId24"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId25"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId26"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId27"/>
+    <sheet name="BPC_SOW_FC_Creation" sheetId="30" r:id="rId3"/>
+    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId4"/>
+    <sheet name="Budget_Redirection" sheetId="15" r:id="rId5"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId6"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId7"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId8"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId9"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId10"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId11"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId14"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId15"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId16"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId17"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId18"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId19"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId20"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId21"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId22"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId23"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId24"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId25"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId26"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId27"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId28"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId29"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -129,9 +132,6 @@
     <t>Congressionaldistrict__c</t>
   </si>
   <si>
-    <t>1st District</t>
-  </si>
-  <si>
     <t>Budget Period Change</t>
   </si>
   <si>
@@ -327,12 +327,6 @@
     <t>fieldCounty__c</t>
   </si>
   <si>
-    <t>Automation Country</t>
-  </si>
-  <si>
-    <t>KA</t>
-  </si>
-  <si>
     <t>fieldState__c</t>
   </si>
   <si>
@@ -355,6 +349,12 @@
   </si>
   <si>
     <t>fieldAddressline2__c</t>
+  </si>
+  <si>
+    <t>fieldRevisedCommitment__c</t>
+  </si>
+  <si>
+    <t>USA</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -817,6 +817,189 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -841,10 +1024,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -852,7 +1035,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -863,7 +1046,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -875,7 +1058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -900,10 +1083,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -911,7 +1094,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -922,7 +1105,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -933,7 +1116,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -944,7 +1127,86 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -969,7 +1231,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -980,10 +1242,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -992,7 +1254,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1018,7 +1280,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1029,10 +1291,10 @@
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1065,10 +1327,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1076,7 +1338,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1087,7 +1349,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1098,7 +1360,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1120,24 +1382,24 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
         <v>68</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
         <v>71</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1170,10 +1432,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1201,312 +1463,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1535,7 +1491,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1546,10 +1502,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1580,6 +1536,312 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1604,10 +1866,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
         <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1615,10 +1877,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1626,10 +1888,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1637,10 +1899,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1648,7 +1910,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1659,7 +1921,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1670,7 +1932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1695,10 +1957,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1706,10 +1968,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" t="s">
         <v>58</v>
-      </c>
-      <c r="C3" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1717,10 +1979,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1728,10 +1990,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1739,7 +2001,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1750,7 +2012,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1761,7 +2023,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1786,10 +2048,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1797,7 +2059,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1808,7 +2070,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1819,7 +2081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1844,7 +2106,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -1855,7 +2117,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1866,10 +2128,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1877,10 +2139,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1888,10 +2150,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1899,14 +2161,22 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7"/>
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1914,9 +2184,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
@@ -1939,7 +2209,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
@@ -1950,7 +2220,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1961,10 +2231,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1972,10 +2242,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1983,10 +2253,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
+        <v>80</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1994,10 +2264,21 @@
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8">
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
@@ -2005,7 +2286,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2030,10 +2311,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2041,10 +2322,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2074,7 +2355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2099,10 +2380,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2132,7 +2413,87 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2157,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2168,10 +2529,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2179,10 +2540,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2190,10 +2551,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2223,7 +2584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2249,7 +2610,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2260,7 +2621,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2271,7 +2632,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2283,7 +2644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2309,10 +2670,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2343,7 +2704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2368,10 +2729,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2379,7 +2740,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2390,7 +2751,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2402,7 +2763,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2427,10 +2857,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2438,7 +2868,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2449,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2460,7 +2890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2551,11 +2981,11 @@
       <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
-        <v>86</v>
+      <c r="B8" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2576,8 +3006,8 @@
       <c r="B10" t="s">
         <v>21</v>
       </c>
-      <c r="C10" t="s">
-        <v>22</v>
+      <c r="C10">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2585,193 +3015,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
-    <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E03F7C9-E210-4E7E-9F06-8E06887498C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39451A82-33A3-406E-8ADF-0A378612B0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="24" activeTab="24" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="102">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>CongressionalDistrict__c</t>
+  </si>
+  <si>
+    <t>SubAmendmentType__c</t>
   </si>
 </sst>
 </file>
@@ -2622,7 +2625,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2633,7 +2636,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2644,7 +2647,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2869,7 +2872,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
         <v>81</v>
@@ -2880,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -2891,7 +2894,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2994,7 +2997,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
         <v>91</v>
@@ -3027,7 +3030,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39451A82-33A3-406E-8ADF-0A378612B0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6C5AEA-1190-4537-9628-9CEE2F2B977B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -3018,8 +3018,8 @@
       <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
-        <v>21</v>
+      <c r="B10" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="C10">
         <v>123</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E6C5AEA-1190-4537-9628-9CEE2F2B977B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE3C946-3B7C-46B6-AF05-6035FAFC3E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1A255A-9E1E-4264-89B4-EBDE4698A8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68903C05-ABC3-4EB5-9660-24A944F52D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="28" activeTab="30" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,7 +750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -761,7 +761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -792,14 +792,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -821,7 +821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -832,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -843,7 +843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -865,7 +865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -876,7 +876,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -887,7 +887,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -898,7 +898,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -917,13 +917,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -945,7 +945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -975,13 +975,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1034,13 +1034,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1103,13 +1103,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1183,13 +1183,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1231,14 +1231,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1279,13 +1279,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1337,13 +1337,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1384,13 +1384,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1443,13 +1443,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1512,13 +1512,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1625,13 +1625,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1771,13 +1771,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1818,13 +1818,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1909,13 +1909,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2000,13 +2000,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2058,13 +2058,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2161,12 +2161,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2251,13 +2251,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2353,13 +2353,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2422,13 +2422,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2502,13 +2502,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2560,13 +2560,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2651,14 +2651,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2711,14 +2711,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2729,18 +2729,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2771,13 +2771,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2830,13 +2830,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2899,13 +2899,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2957,14 +2957,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68903C05-ABC3-4EB5-9660-24A944F52D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACA0E66-036E-442A-8122-3E3ABB567701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="4" activeTab="4" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1A255A-9E1E-4264-89B4-EBDE4698A8E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160B91F3-1FF7-4155-A523-52E619760C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="28" activeTab="30" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="23" activeTab="26" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,7 +750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -761,7 +761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -792,14 +792,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -821,7 +821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -832,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -843,7 +843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -865,7 +865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -876,7 +876,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -887,7 +887,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -898,7 +898,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -917,13 +917,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -945,7 +945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -975,13 +975,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1034,13 +1034,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1103,13 +1103,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1183,13 +1183,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1231,14 +1231,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1279,13 +1279,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1337,13 +1337,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1384,13 +1384,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1443,13 +1443,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1512,13 +1512,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1625,13 +1625,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1771,13 +1771,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1818,13 +1818,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1909,13 +1909,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2000,13 +2000,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2058,13 +2058,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2161,12 +2161,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2251,13 +2251,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2353,13 +2353,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2422,13 +2422,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2502,13 +2502,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2560,13 +2560,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2651,14 +2651,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2711,14 +2711,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2771,13 +2771,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2830,13 +2830,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2899,13 +2899,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2957,14 +2957,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACA0E66-036E-442A-8122-3E3ABB567701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE493FFD-EAD4-42D5-B147-5B6D70EC45C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="28" activeTab="28" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ACA0E66-036E-442A-8122-3E3ABB567701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA7ECF8-BEA1-4E66-8F6B-38F25ACAEC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="6" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -733,13 +733,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.109375" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,7 +750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -761,7 +761,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -772,7 +772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -792,14 +792,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -821,7 +821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -832,7 +832,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -843,7 +843,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -854,7 +854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -865,7 +865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -876,7 +876,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -887,7 +887,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -898,7 +898,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -917,13 +917,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -945,7 +945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -956,7 +956,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -975,13 +975,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1034,13 +1034,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1103,13 +1103,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1183,13 +1183,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1211,7 +1211,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1231,14 +1231,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1279,13 +1279,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1307,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1337,13 +1337,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1384,13 +1384,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1443,13 +1443,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,7 +1460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1471,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1512,13 +1512,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1625,13 +1625,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1708,7 +1708,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1771,13 +1771,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1818,13 +1818,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1857,7 +1857,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1909,13 +1909,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1959,7 +1959,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2000,13 +2000,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2058,13 +2058,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2161,12 +2161,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2221,7 +2221,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2251,13 +2251,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2353,13 +2353,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2381,7 +2381,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2422,13 +2422,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2502,13 +2502,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2560,13 +2560,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2621,7 +2621,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2651,14 +2651,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2711,14 +2711,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2771,13 +2771,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2799,7 +2799,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2810,7 +2810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2830,13 +2830,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2899,13 +2899,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2927,7 +2927,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2957,14 +2957,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2975,7 +2975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2986,7 +2986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2997,7 +2997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3030,7 +3030,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA7ECF8-BEA1-4E66-8F6B-38F25ACAEC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F932A02-FF3D-4191-A828-17EC997092E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="14" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -27,23 +27,24 @@
     <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
     <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
     <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId14"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId15"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId16"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId17"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId18"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId19"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId20"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId21"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId22"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId23"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId24"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId25"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId26"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId27"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId28"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId29"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId30"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId31"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="33" r:id="rId15"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId16"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId17"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId18"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId19"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId20"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId21"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId22"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId23"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId24"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId25"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId26"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId27"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId28"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId29"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId30"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId31"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId32"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="93">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -335,6 +336,15 @@
   </si>
   <si>
     <t>Congressionaldistrict__c</t>
+  </si>
+  <si>
+    <t>ContactChangeDescription__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>Justification__c</t>
   </si>
 </sst>
 </file>
@@ -1181,6 +1191,153 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E45A06C-BA03-457E-884E-B76F9818692C}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.88671875" customWidth="1"/>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="35.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1228,7 +1385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1276,7 +1433,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1334,7 +1491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1378,65 +1535,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1510,6 +1608,65 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1622,7 +1779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1768,7 +1925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1815,7 +1972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1906,7 +2063,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1997,7 +2154,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2055,7 +2212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2158,7 +2315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2248,7 +2405,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2343,75 +2500,6 @@
       </c>
       <c r="C8">
         <v>3000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2500,6 +2588,75 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2557,7 +2714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OldLaptopBackup\ProductLWC_Govgrants\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE493FFD-EAD4-42D5-B147-5B6D70EC45C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380CD50A-7A13-42F8-A79B-4314B68004B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="28" activeTab="28" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="25" activeTab="27" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="89">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -332,9 +332,6 @@
   </si>
   <si>
     <t>InternalOrganization__c</t>
-  </si>
-  <si>
-    <t>Congressionaldistrict__c</t>
   </si>
 </sst>
 </file>
@@ -733,13 +730,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -750,7 +747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -761,7 +758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -772,7 +769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -792,14 +789,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -810,7 +807,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -821,7 +818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -832,7 +829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -843,7 +840,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -854,7 +851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -865,7 +862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -876,7 +873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -887,7 +884,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -898,7 +895,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -917,13 +914,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -934,7 +931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -945,7 +942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -956,7 +953,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -975,13 +972,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -992,7 +989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1003,7 +1000,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1014,7 +1011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1034,13 +1031,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1051,7 +1048,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1062,7 +1059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1073,7 +1070,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1084,7 +1081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1103,13 +1100,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1120,7 +1117,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1131,7 +1128,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1142,7 +1139,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1153,7 +1150,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1164,7 +1161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1183,13 +1180,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1200,7 +1197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1211,7 +1208,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1231,14 +1228,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1260,7 +1257,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1279,13 +1276,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1296,7 +1293,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1307,7 +1304,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1318,7 +1315,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1337,13 +1334,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1365,7 +1362,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1384,13 +1381,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1412,7 +1409,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1423,7 +1420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1443,13 +1440,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,7 +1457,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1471,7 +1468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1482,7 +1479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1493,7 +1490,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1512,13 +1509,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1540,7 +1537,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1551,7 +1548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1562,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1573,7 +1570,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1584,7 +1581,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1595,7 +1592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1606,7 +1603,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1625,13 +1622,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1642,7 +1639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1653,7 +1650,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1664,7 +1661,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1675,7 +1672,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1686,7 +1683,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1694,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1708,7 +1705,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1719,7 +1716,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1730,7 +1727,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1741,7 +1738,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1752,7 +1749,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1771,13 +1768,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1799,7 +1796,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1818,13 +1815,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1835,7 +1832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1846,7 +1843,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1857,7 +1854,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1868,7 +1865,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1879,7 +1876,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1890,7 +1887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1909,13 +1906,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1937,7 +1934,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1948,7 +1945,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1959,7 +1956,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1970,7 +1967,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1981,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2000,13 +1997,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2017,7 +2014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2028,7 +2025,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2039,7 +2036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2058,13 +2055,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2075,7 +2072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2086,7 +2083,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2097,7 +2094,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2108,7 +2105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2119,7 +2116,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2130,7 +2127,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2141,7 +2138,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2161,12 +2158,12 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2177,7 +2174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2188,7 +2185,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2199,7 +2196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2210,7 +2207,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2221,7 +2218,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2232,7 +2229,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2251,13 +2248,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2268,7 +2265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2279,7 +2276,7 @@
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2290,7 +2287,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2301,7 +2298,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2312,18 +2309,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2334,7 +2331,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2353,13 +2350,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2370,7 +2367,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2381,7 +2378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2392,7 +2389,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2422,13 +2419,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2439,7 +2436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2450,7 +2447,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2461,7 +2458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2472,7 +2469,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2483,7 +2480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2502,13 +2499,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2519,7 +2516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2530,7 +2527,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2541,7 +2538,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2560,13 +2557,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2577,7 +2574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2588,7 +2585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2599,7 +2596,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2610,7 +2607,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2621,7 +2618,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2632,7 +2629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2651,14 +2648,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2669,7 +2666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2680,7 +2677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2691,7 +2688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2711,14 +2708,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2729,7 +2726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2740,7 +2737,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2751,7 +2748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2771,13 +2768,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2799,7 +2796,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2810,7 +2807,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2830,13 +2827,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2847,7 +2844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2858,7 +2855,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2869,7 +2866,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2880,7 +2877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2899,13 +2896,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2916,7 +2913,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2927,7 +2924,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2938,7 +2935,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2957,14 +2954,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2975,7 +2972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2986,7 +2983,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2997,7 +2994,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3008,7 +3005,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3019,7 +3016,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3030,7 +3027,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3041,7 +3038,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3052,7 +3049,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3063,7 +3060,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3074,7 +3071,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380CD50A-7A13-42F8-A79B-4314B68004B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E205FB49-BBBC-4E04-893B-030C51A7D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="25" activeTab="27" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="29" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -289,9 +289,6 @@
     <t>Carry Forward</t>
   </si>
   <si>
-    <t>LA</t>
-  </si>
-  <si>
     <t>VA</t>
   </si>
   <si>
@@ -332,6 +329,9 @@
   </si>
   <si>
     <t>InternalOrganization__c</t>
+  </si>
+  <si>
+    <t>LA: Louisiana</t>
   </si>
 </sst>
 </file>
@@ -867,7 +867,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>19</v>
@@ -889,7 +889,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <v>123</v>
@@ -900,10 +900,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -1053,7 +1053,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -1064,7 +1064,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1122,7 +1122,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
@@ -1133,7 +1133,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1144,7 +1144,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>72</v>
@@ -1202,7 +1202,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1213,7 +1213,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>50</v>
@@ -1251,7 +1251,7 @@
         <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2">
         <v>70</v>
@@ -1262,7 +1262,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
         <v>50</v>
@@ -1298,7 +1298,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>73</v>
@@ -1586,7 +1586,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -2058,7 +2058,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -2077,7 +2077,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -2088,7 +2088,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -2099,7 +2099,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -2110,10 +2110,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2121,7 +2121,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2132,10 +2132,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2143,7 +2143,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2161,6 +2161,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -2179,7 +2180,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
@@ -2190,7 +2191,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
@@ -2201,10 +2202,10 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -2212,7 +2213,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>123</v>
@@ -2223,10 +2224,10 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -2234,7 +2235,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7">
         <v>2000</v>
@@ -2252,6 +2253,7 @@
   <cols>
     <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -2270,7 +2272,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
@@ -2281,7 +2283,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -2292,7 +2294,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -2303,10 +2305,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -2314,7 +2316,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6">
         <v>123</v>
@@ -2325,10 +2327,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -2336,7 +2338,7 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2671,7 +2673,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -2731,7 +2733,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
@@ -2790,7 +2792,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
@@ -2849,7 +2851,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>71</v>
@@ -2860,7 +2862,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>73</v>
@@ -2918,7 +2920,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>72</v>
@@ -3043,10 +3045,10 @@
         <v>12</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -3065,7 +3067,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C10">
         <v>123</v>
@@ -3076,7 +3078,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
         <v>19</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E205FB49-BBBC-4E04-893B-030C51A7D6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC8C55-9A70-4283-A75F-7BC65FFFD662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="29" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -27,23 +27,25 @@
     <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
     <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
     <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId14"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId15"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId16"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId17"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId18"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId19"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId20"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId21"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId22"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId23"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId24"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId25"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId26"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId27"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId28"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId29"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId30"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId31"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId15"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId16"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId17"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId18"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId19"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId20"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId21"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId22"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId23"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId24"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId25"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId26"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId27"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId28"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId29"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId30"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId31"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId32"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId33"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="91">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -332,6 +334,12 @@
   </si>
   <si>
     <t>LA: Louisiana</t>
+  </si>
+  <si>
+    <t>ContactChangeDescription__c</t>
+  </si>
+  <si>
+    <t>Justification__c</t>
   </si>
 </sst>
 </file>
@@ -730,13 +738,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.1796875" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -747,7 +755,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -758,7 +766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -769,7 +777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -789,14 +797,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.453125" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -807,7 +815,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -818,7 +826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -829,7 +837,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -840,7 +848,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -851,7 +859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -862,7 +870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -873,7 +881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -884,7 +892,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -895,7 +903,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -914,13 +922,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -931,7 +939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -942,7 +950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -953,7 +961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -972,13 +980,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -989,7 +997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1000,7 +1008,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1011,7 +1019,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1031,13 +1039,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1048,7 +1056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1059,7 +1067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1070,7 +1078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1081,7 +1089,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1100,13 +1108,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1128,7 +1136,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1139,7 +1147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1150,7 +1158,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1161,7 +1169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1178,15 +1186,24 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,7 +1214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1208,7 +1225,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1225,17 +1242,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1246,7 +1263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1257,7 +1274,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1273,16 +1290,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1293,7 +1310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1304,7 +1321,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1315,7 +1332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1331,16 +1348,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1351,7 +1368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>64</v>
       </c>
@@ -1362,7 +1379,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>64</v>
       </c>
@@ -1375,78 +1392,19 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1457,7 +1415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1468,7 +1426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1479,7 +1437,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1490,7 +1448,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1507,15 +1465,74 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1526,7 +1543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1537,7 +1554,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1548,7 +1565,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1559,7 +1576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1570,7 +1587,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1581,7 +1598,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1592,7 +1609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1603,7 +1620,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1619,16 +1636,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1656,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1650,7 +1667,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1661,7 +1678,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1672,7 +1689,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1683,7 +1700,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1694,7 +1711,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1705,7 +1722,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1716,7 +1733,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1727,7 +1744,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1738,7 +1755,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1749,7 +1766,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -1765,16 +1782,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1785,7 +1802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1796,7 +1813,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1812,16 +1829,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1832,7 +1849,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1843,7 +1860,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1854,7 +1871,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1865,7 +1882,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1876,7 +1893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1887,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1903,16 +1920,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1923,7 +1940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1934,7 +1951,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1945,7 +1962,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1956,7 +1973,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1967,7 +1984,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1978,7 +1995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1994,16 +2011,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2014,7 +2031,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2025,7 +2042,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2036,7 +2053,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2052,16 +2069,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2072,7 +2089,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2083,7 +2100,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2094,7 +2111,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2105,7 +2122,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2116,7 +2133,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2127,7 +2144,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2138,7 +2155,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2155,16 +2172,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2175,7 +2192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2186,7 +2203,7 @@
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2197,7 +2214,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2208,7 +2225,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2219,7 +2236,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2230,7 +2247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2246,17 +2263,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2267,7 +2284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2278,7 +2295,7 @@
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2289,7 +2306,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -2300,7 +2317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2311,7 +2328,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2322,7 +2339,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2333,7 +2350,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -2342,75 +2359,6 @@
       </c>
       <c r="C8">
         <v>3000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2421,13 +2369,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2438,7 +2386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2449,7 +2397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2460,7 +2408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2471,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2482,7 +2430,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2499,15 +2447,84 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2518,7 +2535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2529,7 +2546,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2540,7 +2557,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2556,16 +2573,74 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2576,7 +2651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2587,7 +2662,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2598,7 +2673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2609,7 +2684,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2620,7 +2695,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2631,7 +2706,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2650,14 +2725,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2668,7 +2743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2679,7 +2754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2690,7 +2765,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2710,14 +2785,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2728,7 +2803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2739,7 +2814,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2750,7 +2825,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2770,13 +2845,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2787,7 +2862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2798,7 +2873,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2809,7 +2884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2829,13 +2904,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2846,7 +2921,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2857,7 +2932,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2868,7 +2943,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2879,7 +2954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2898,13 +2973,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2915,7 +2990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2926,7 +3001,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2937,7 +3012,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2956,14 +3031,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2974,7 +3049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2985,7 +3060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2996,7 +3071,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3007,7 +3082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3018,7 +3093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -3029,7 +3104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -3040,7 +3115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3051,7 +3126,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -3062,7 +3137,7 @@
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -3073,7 +3148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Auto_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98AA166-91E0-4F58-92C0-14DCADB4A3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84404813-B2CF-4FC0-9190-0C56B4E4C79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="8" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="106">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -99,9 +99,6 @@
     <t>ScopeofWorkChangeDescription__c</t>
   </si>
   <si>
-    <t>Automation Justification for Scope of Work Change</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
@@ -355,6 +352,36 @@
   </si>
   <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>Scope of Work Change Purpose</t>
+  </si>
+  <si>
+    <t>Scope of Work Change Impact</t>
+  </si>
+  <si>
+    <t>Department of health Overall Justification</t>
+  </si>
+  <si>
+    <t>Department of health Overall Impact</t>
+  </si>
+  <si>
+    <t>Departmental Justification for Scope of Work Change</t>
+  </si>
+  <si>
+    <t>441 4th Street, NW, Suite 715 North</t>
+  </si>
+  <si>
+    <t>McMahon Dr #200</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Bernalillo</t>
+  </si>
+  <si>
+    <t>fieldZipCode4Extension__c</t>
   </si>
 </sst>
 </file>
@@ -463,9 +490,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -503,7 +530,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -609,7 +636,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -751,7 +778,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -760,13 +787,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -777,18 +804,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -796,10 +823,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -807,7 +834,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -819,14 +846,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.42578125" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -837,103 +864,103 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="C5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
       </c>
       <c r="C8">
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -944,13 +971,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -961,18 +988,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -983,7 +1010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1002,13 +1029,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1019,34 +1046,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1061,13 +1088,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,45 +1105,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1130,12 +1157,12 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,56 +1173,56 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -1209,13 +1236,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1226,26 +1253,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1257,14 +1284,14 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1275,26 +1302,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1305,13 +1332,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1322,34 +1349,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1363,13 +1390,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1380,26 +1407,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" t="s">
         <v>67</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>68</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1410,13 +1437,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,18 +1454,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1449,7 +1476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1469,13 +1496,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1486,29 +1513,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1519,7 +1546,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1538,13 +1565,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1555,92 +1582,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
       </c>
       <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1651,13 +1678,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1668,125 +1695,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>49</v>
       </c>
-      <c r="C11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1797,13 +1824,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1814,23 +1841,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>53</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1844,13 +1871,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1861,67 +1888,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>62</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1935,13 +1962,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1952,67 +1979,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
         <v>57</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>59</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>61</v>
       </c>
-      <c r="C5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>62</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>63</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -2026,13 +2053,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2043,34 +2070,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2084,13 +2111,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2101,78 +2128,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>87</v>
       </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2187,13 +2214,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2204,78 +2231,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>87</v>
       </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2289,13 +2316,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2306,29 +2333,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2339,7 +2366,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2358,13 +2385,13 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2375,18 +2402,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2397,7 +2424,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2416,13 +2443,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2433,40 +2460,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2477,7 +2504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2496,13 +2523,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2513,51 +2540,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
       <c r="C4" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2568,7 +2595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2587,14 +2614,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2605,34 +2632,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2647,14 +2674,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2665,18 +2692,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2687,7 +2714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2707,13 +2734,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2724,34 +2751,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2766,13 +2793,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2783,45 +2810,45 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -2835,13 +2862,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2852,34 +2879,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -2892,15 +2919,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2911,117 +2938,129 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>86</v>
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12">
+        <v>9955</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC8C55-9A70-4283-A75F-7BC65FFFD662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD8ECB9-9439-4C36-BEAA-D7BE25520C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="101">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -102,9 +102,6 @@
     <t>ScopeofWorkChangeDescription__c</t>
   </si>
   <si>
-    <t>Automation Justification for Scope of Work Change</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
@@ -340,6 +337,39 @@
   </si>
   <si>
     <t>Justification__c</t>
+  </si>
+  <si>
+    <t>Department of health Overall Justification</t>
+  </si>
+  <si>
+    <t>Department of health Overall Impact</t>
+  </si>
+  <si>
+    <t>Departmental Justification for Scope of Work Change</t>
+  </si>
+  <si>
+    <t>441 4th Street, NW, Suite 715 North</t>
+  </si>
+  <si>
+    <t>McMahon Dr #200</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Congressionaldistrict__c</t>
+  </si>
+  <si>
+    <t>Bernalillo</t>
+  </si>
+  <si>
+    <t>ZipCode4Extension__c</t>
+  </si>
+  <si>
+    <t>Scope of Work Change Purpose</t>
+  </si>
+  <si>
+    <t>Scope of Work Change Impact</t>
   </si>
 </sst>
 </file>
@@ -406,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -423,6 +453,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,13 +771,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{236FB0C8-BA27-46AC-83FF-CF70FBE95475}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" customWidth="1"/>
     <col min="3" max="3" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,18 +788,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -774,10 +807,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -785,7 +818,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -797,14 +830,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" customWidth="1"/>
     <col min="3" max="3" width="44" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -815,9 +848,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>10</v>
@@ -826,9 +859,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -837,81 +870,81 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
       </c>
       <c r="C8">
         <v>12345</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9">
         <v>123</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -922,13 +955,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -939,18 +972,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -961,7 +994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -980,13 +1013,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -997,18 +1030,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1019,7 +1052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1039,13 +1072,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1056,29 +1089,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1108,13 +1141,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1125,40 +1158,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1202,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1188,7 +1221,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1197,13 +1230,13 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1214,26 +1247,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1245,14 +1278,14 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1263,26 +1296,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1293,13 +1326,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1310,18 +1343,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1332,7 +1365,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1351,13 +1384,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1368,26 +1401,26 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1398,13 +1431,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1415,29 +1448,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1448,7 +1481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1467,13 +1500,13 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1484,18 +1517,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1506,7 +1539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1526,13 +1559,13 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1543,92 +1576,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
       </c>
       <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1639,13 +1672,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1656,125 +1689,125 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="s">
         <v>41</v>
       </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1785,13 +1818,13 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1802,23 +1835,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
       </c>
       <c r="C3">
         <v>3650</v>
@@ -1832,13 +1865,13 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1849,67 +1882,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -1923,13 +1956,13 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1940,67 +1973,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="s">
         <v>55</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
       </c>
       <c r="C7">
         <v>3650</v>
@@ -2014,13 +2047,13 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2031,18 +2064,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2053,7 +2086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2072,13 +2105,13 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2089,78 +2122,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="C5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C8">
         <v>2000</v>
@@ -2175,13 +2208,13 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2192,67 +2225,67 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="5">
         <v>4017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="C4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C7">
         <v>2000</v>
@@ -2266,14 +2299,14 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2284,78 +2317,78 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C2" s="5">
         <v>6017</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>82</v>
-      </c>
       <c r="C5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6">
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="C8">
         <v>3000</v>
@@ -2369,13 +2402,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2386,40 +2419,40 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2430,7 +2463,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2449,13 +2482,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2466,29 +2499,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2499,7 +2532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2518,13 +2551,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2535,18 +2568,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2557,7 +2590,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2576,13 +2609,13 @@
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="2" max="2" width="34.453125" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2593,37 +2626,37 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>89</v>
       </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
-      </c>
       <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2634,13 +2667,13 @@
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2651,51 +2684,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
       <c r="C4" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2706,7 +2739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2725,14 +2758,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2743,18 +2776,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2765,7 +2798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2785,14 +2818,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2803,18 +2836,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2825,7 +2858,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2845,13 +2878,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2862,18 +2895,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2884,7 +2917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2904,13 +2937,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2921,29 +2954,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2954,7 +2987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2973,13 +3006,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2990,18 +3023,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -3012,7 +3045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -3030,133 +3063,144 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
       <c r="C5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
       <c r="C6" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
+        <v>19</v>
+      </c>
+      <c r="C9" s="8">
         <v>12345</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10">
+        <v>96</v>
+      </c>
+      <c r="C10" s="8">
         <v>123</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>81</v>
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="8">
+        <v>9955</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC8C55-9A70-4283-A75F-7BC65FFFD662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391D2905-5AE4-494C-9F31-03058660E481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="23" activeTab="25" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC8C55-9A70-4283-A75F-7BC65FFFD662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430042AA-F6BF-4E24-AF80-BFA5A87B9F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="5760" yWindow="1296" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -33,19 +33,20 @@
     <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId18"/>
     <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId19"/>
     <sheet name="FundingChange_Creation" sheetId="5" r:id="rId20"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId21"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId22"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId23"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId24"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId25"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId26"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId27"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId28"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId29"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId30"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId31"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId32"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId33"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId21"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId22"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId23"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId24"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId25"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId26"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId27"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId28"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId29"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId30"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId31"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId32"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId33"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId34"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -340,13 +341,22 @@
   </si>
   <si>
     <t>Justification__c</t>
+  </si>
+  <si>
+    <t>GranteeAmendmentType__c</t>
+  </si>
+  <si>
+    <t>InitiatedByGrantee__c</t>
+  </si>
+  <si>
+    <t>Grantee</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,6 +395,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -406,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -423,6 +439,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1524,6 +1541,75 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1636,7 +1722,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1782,7 +1868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1829,7 +1915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1920,7 +2006,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2011,7 +2097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2069,7 +2155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2172,7 +2258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2263,7 +2349,87 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2366,9 +2532,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -2394,7 +2560,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2405,7 +2571,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2413,10 +2579,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2424,98 +2590,18 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2573,7 +2659,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2631,7 +2717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430042AA-F6BF-4E24-AF80-BFA5A87B9F62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE2C14A-DADB-4422-90C5-C2A6B71E308A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="1296" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -1606,6 +1606,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FE2C14A-DADB-4422-90C5-C2A6B71E308A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F22EE5-BF44-470D-90CC-F6E5A51C29F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -18,35 +18,36 @@
     <sheet name="BPC_SOW_FC_Creation" sheetId="30" r:id="rId3"/>
     <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId4"/>
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId5"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId6"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId7"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId8"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId9"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId10"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId11"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId14"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId15"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId16"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId17"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId18"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId19"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId20"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId21"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId22"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId23"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId24"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId25"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId26"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId27"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId28"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId29"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId30"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId31"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId32"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId33"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId34"/>
+    <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId6"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId7"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId8"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId9"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId10"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId11"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId12"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId13"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId14"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId16"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId17"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId18"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId19"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId20"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId21"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId22"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId23"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId24"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId25"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId26"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId27"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId28"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId29"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId30"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId31"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId32"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId33"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId34"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -350,6 +351,9 @@
   </si>
   <si>
     <t>Grantee</t>
+  </si>
+  <si>
+    <t>Grantor</t>
   </si>
 </sst>
 </file>
@@ -812,6 +816,142 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -936,7 +1076,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -994,7 +1134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1053,7 +1193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1122,7 +1262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1202,7 +1342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1211,7 +1351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1259,7 +1399,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1307,7 +1447,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1365,7 +1505,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1412,9 +1621,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
-  <dimension ref="A1:C5"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -1440,7 +1649,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1448,10 +1657,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1459,7 +1668,66 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1469,11 +1737,271 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1481,8 +2009,237 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1509,7 +2266,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1536,17 +2293,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
-  <dimension ref="A1:C5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1562,545 +2318,90 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -2126,7 +2427,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2134,10 +2435,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2145,121 +2446,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>82</v>
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <v>2000</v>
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2350,87 +2570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2533,7 +2673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2602,7 +2742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2660,7 +2800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2718,7 +2858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2930,6 +3070,75 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6200C95B-DC25-4512-B73E-2D04804A2197}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="31.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2988,7 +3197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3057,7 +3266,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3113,140 +3322,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F22EE5-BF44-470D-90CC-F6E5A51C29F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30398E0B-64DD-497F-88CD-863013865DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="5" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -348,9 +348,6 @@
   </si>
   <si>
     <t>InitiatedByGrantee__c</t>
-  </si>
-  <si>
-    <t>Grantee</t>
   </si>
   <si>
     <t>Grantor</t>
@@ -3108,7 +3105,7 @@
         <v>92</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC8C55-9A70-4283-A75F-7BC65FFFD662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30398E0B-64DD-497F-88CD-863013865DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -18,34 +18,36 @@
     <sheet name="BPC_SOW_FC_Creation" sheetId="30" r:id="rId3"/>
     <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId4"/>
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId5"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId6"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId7"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId8"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId9"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId10"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId11"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId12"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId13"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId14"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId15"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId16"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId17"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId18"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId19"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId20"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId21"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId22"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId23"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId24"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId25"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId26"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId27"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId28"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId29"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId30"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId31"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId32"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId33"/>
+    <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId6"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId7"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId8"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId9"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId10"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId11"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId12"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId13"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId14"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId15"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId16"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId17"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId18"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId19"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId20"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId21"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId22"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId23"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId24"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId25"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId26"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId27"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId28"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId29"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId30"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId31"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId32"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId33"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId34"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId35"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -340,13 +342,22 @@
   </si>
   <si>
     <t>Justification__c</t>
+  </si>
+  <si>
+    <t>GranteeAmendmentType__c</t>
+  </si>
+  <si>
+    <t>InitiatedByGrantee__c</t>
+  </si>
+  <si>
+    <t>Grantor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,6 +396,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -406,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -423,6 +440,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -795,6 +813,142 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -919,7 +1073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -977,7 +1131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1036,7 +1190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1105,7 +1259,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1185,7 +1339,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1194,7 +1348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1242,7 +1396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1290,7 +1444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1348,7 +1502,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1395,9 +1618,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
-  <dimension ref="A1:C5"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -1423,7 +1646,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1431,10 +1654,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1442,7 +1665,66 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1452,11 +1734,271 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1464,8 +2006,237 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1492,7 +2263,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1519,17 +2290,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1543,477 +2313,92 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -2039,7 +2424,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2047,10 +2432,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2058,121 +2443,40 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>82</v>
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <v>2000</v>
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2263,7 +2567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2366,9 +2670,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -2394,7 +2698,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -2405,7 +2709,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2413,10 +2717,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2424,98 +2728,18 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2573,7 +2797,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2631,7 +2855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2843,6 +3067,75 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6200C95B-DC25-4512-B73E-2D04804A2197}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="3" max="3" width="31.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2901,7 +3194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2970,7 +3263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3026,140 +3319,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,46 +8,47 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30398E0B-64DD-497F-88CD-863013865DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC4EC48-62E5-44C4-8108-F6FBC38E5C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Scope&amp;BudgetPeriod_Creation" sheetId="25" r:id="rId2"/>
-    <sheet name="BPC_SOW_FC_Creation" sheetId="30" r:id="rId3"/>
-    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId4"/>
-    <sheet name="Budget_Redirection" sheetId="15" r:id="rId5"/>
-    <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId6"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId7"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId8"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId9"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId10"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId11"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId12"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId13"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId14"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId15"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId16"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId17"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId18"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId19"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId20"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId21"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId22"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId23"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId24"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId25"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId26"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId27"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId28"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId29"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId30"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId31"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId32"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId33"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId34"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId35"/>
+    <sheet name="Grantee_ScopeOfWork_Creation" sheetId="37" r:id="rId2"/>
+    <sheet name="Scope&amp;BudgetPeriod_Creation" sheetId="25" r:id="rId3"/>
+    <sheet name="BPC_SOW_FC_Creation" sheetId="30" r:id="rId4"/>
+    <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId5"/>
+    <sheet name="Budget_Redirection" sheetId="15" r:id="rId6"/>
+    <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId7"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId8"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId9"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId10"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId11"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId12"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId13"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId14"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId15"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId16"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId17"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId18"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId19"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId20"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId21"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId22"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId23"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId24"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId25"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId26"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId27"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId28"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId29"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId30"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId31"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId32"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId33"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId34"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId35"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId36"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -813,6 +814,64 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -948,7 +1007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1073,7 +1132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1131,7 +1190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1190,7 +1249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1259,7 +1318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1339,7 +1398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1348,7 +1407,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1396,7 +1455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1444,7 +1503,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEC1918-8771-4526-A90D-55EE42978FB3}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1502,7 +1630,729 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADA2F6C6-D2C2-45C9-9867-EB743A8A318E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1571,104 +2421,101 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
@@ -1677,13 +2524,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1699,860 +2546,61 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="C5">
-        <v>3650</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8">
-        <v>2000</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -2567,7 +2615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2670,7 +2718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2739,7 +2787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2797,7 +2845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2855,7 +2903,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2947,6 +2995,86 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3006,7 +3134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CED252CC-9A41-43A8-97A3-527BD171EFF4}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3066,7 +3194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6200C95B-DC25-4512-B73E-2D04804A2197}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3135,7 +3263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3194,7 +3322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3261,62 +3389,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC4EC48-62E5-44C4-8108-F6FBC38E5C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBD2137-D85A-41F9-88C0-DBEC68D8E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BBD2137-D85A-41F9-88C0-DBEC68D8E061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4EC4AD-9144-466A-8D66-DD7891D84333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -20,35 +20,37 @@
     <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId5"/>
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId6"/>
     <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId7"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId8"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId9"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId10"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId11"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId12"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId13"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId14"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId15"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId16"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId17"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId18"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId19"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId20"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId21"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId22"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId23"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId24"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId25"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId26"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId27"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId28"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId29"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId30"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId31"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId32"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId33"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId34"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId35"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId36"/>
+    <sheet name="Grantee_PeriodicRenewal" sheetId="38" r:id="rId8"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId9"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId10"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId11"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId12"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId13"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId14"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId15"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId16"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId17"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId18"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId19"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId20"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId21"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId22"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId23"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId24"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId25"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId26"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId27"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId28"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId29"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId30"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId31"/>
+    <sheet name="GranteePeriodic Renewal Edition" sheetId="39" r:id="rId32"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId33"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId34"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId35"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId36"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId37"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -352,6 +354,9 @@
   </si>
   <si>
     <t>Grantor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -814,6 +819,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -871,7 +945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1007,7 +1081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1132,7 +1206,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1190,7 +1264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1249,7 +1323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1318,7 +1392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1398,7 +1472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1407,7 +1481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1455,7 +1529,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEC1918-8771-4526-A90D-55EE42978FB3}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1503,13 +1646,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEC1918-8771-4526-A90D-55EE42978FB3}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1527,11 +1670,175 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="8" t="s">
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1569,16 +1876,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1592,15 +1900,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1608,10 +1916,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1619,71 +1927,79 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1702,10 +2018,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1713,10 +2029,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1724,25 +2040,112 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1758,24 +2161,71 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1783,36 +2233,57 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
+      <c r="B5" t="s">
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1826,15 +2297,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1842,10 +2313,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1853,10 +2324,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1864,10 +2335,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1875,476 +2346,21 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7">
         <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2422,6 +2438,64 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2524,7 +2598,55 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2615,7 +2737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2718,7 +2840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2787,7 +2909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2845,7 +2967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2903,7 +3025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3196,13 +3318,87 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6200C95B-DC25-4512-B73E-2D04804A2197}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.109375" customWidth="1"/>
     <col min="3" max="3" width="31.77734375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D310988B-E440-4454-8C00-9494A30674CD}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.109375" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
@@ -3222,7 +3418,7 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3263,7 +3459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3320,73 +3516,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="27.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4EC4AD-9144-466A-8D66-DD7891D84333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4A50F1-1201-4D39-A0FA-625EE8E77474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="29" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId29"/>
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId30"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId31"/>
-    <sheet name="GranteePeriodic Renewal Edition" sheetId="39" r:id="rId32"/>
+    <sheet name="Grantee PeriodicRenewal Edition" sheetId="39" r:id="rId32"/>
     <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId33"/>
     <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId34"/>
     <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId35"/>
@@ -2638,7 +2638,7 @@
         <v>80</v>
       </c>
       <c r="C3">
-        <v>1000</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A4A50F1-1201-4D39-A0FA-625EE8E77474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8145D33B-A2C5-41EA-9673-F4B60E5D3841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="29" activeTab="31" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="5760" yWindow="2688" windowWidth="17280" windowHeight="8880" firstSheet="7" activeTab="7" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Subrecipient_SOW_creation" sheetId="17" r:id="rId5"/>
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId6"/>
     <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId7"/>
-    <sheet name="Grantee_PeriodicRenewal" sheetId="38" r:id="rId8"/>
+    <sheet name="Grantee_PRenewal_Creation" sheetId="38" r:id="rId8"/>
     <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId9"/>
     <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId10"/>
     <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId11"/>
@@ -44,7 +44,7 @@
     <sheet name="Progress Report Schedule" sheetId="10" r:id="rId29"/>
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId30"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId31"/>
-    <sheet name="Grantee PeriodicRenewal Edition" sheetId="39" r:id="rId32"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId32"/>
     <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId33"/>
     <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId34"/>
     <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId35"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8145D33B-A2C5-41EA-9673-F4B60E5D3841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60007A36-4428-46E4-AA6D-FA836BEFE933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2688" windowWidth="17280" windowHeight="8880" firstSheet="7" activeTab="7" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="5760" yWindow="2688" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -27,30 +27,32 @@
     <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId12"/>
     <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId13"/>
     <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId14"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId15"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId16"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId17"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId18"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId19"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId20"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId21"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId22"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId23"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId24"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId25"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId26"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId27"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId28"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId29"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId30"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId31"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId32"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId33"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId34"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId35"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId36"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId37"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId38"/>
+    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId15"/>
+    <sheet name="Sheet3" sheetId="41" r:id="rId16"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId17"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId18"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId19"/>
+    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId20"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId21"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId22"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId23"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId24"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId25"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId26"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId27"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId28"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId29"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId30"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId31"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId32"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId33"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId34"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId35"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId36"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId37"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId38"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId39"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1265,6 +1267,84 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A04F876-0CD3-4EAF-9941-AF87F65CFA3E}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AD510-703D-495D-9F32-51DAD0BC6535}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1323,7 +1403,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1392,7 +1472,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1469,63 +1549,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1599,6 +1622,102 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1646,7 +1765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1704,7 +1823,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1751,7 +1870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1810,7 +1929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1880,7 +1999,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1993,7 +2112,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2139,7 +2258,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2178,188 +2297,6 @@
         <v>52</v>
       </c>
       <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
         <v>3650</v>
       </c>
     </row>
@@ -2438,6 +2375,188 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2495,7 +2614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2598,7 +2717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2646,7 +2765,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2737,7 +2856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2840,7 +2959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2909,7 +3028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2967,7 +3086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3018,97 +3137,6 @@
       </c>
       <c r="C4" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3196,6 +3224,97 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60007A36-4428-46E4-AA6D-FA836BEFE933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32E782A-4912-4C4F-9D9A-5A060A6E32A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2688" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -1650,7 +1650,7 @@
         <v>77</v>
       </c>
       <c r="C2">
-        <v>70</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32E782A-4912-4C4F-9D9A-5A060A6E32A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084E9BD6-5E43-44C7-A877-8C0A5F54A7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="19" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="14" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -1271,7 +1271,7 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
     <col min="3" max="3" width="31.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1290,8 +1290,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="C2" t="s">
         <v>21</v>
@@ -1313,7 +1313,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
@@ -1323,8 +1323,8 @@
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
-        <v>7</v>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC4EC48-62E5-44C4-8108-F6FBC38E5C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E1ECFE-F7C1-487F-B0B4-333116DBA707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="30" activeTab="32" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -44,11 +44,13 @@
     <sheet name="Periodic Renewal" sheetId="12" r:id="rId29"/>
     <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId30"/>
     <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId31"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId32"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId33"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId34"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId35"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId36"/>
+    <sheet name="Grantee_PRenewal_Creation" sheetId="38" r:id="rId32"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId33"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId34"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId35"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId36"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId37"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -2616,6 +2618,121 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D37BD41-3509-4274-A8BB-C767D9F8146D}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6446ACD1-050C-4595-A324-AF366517EC90}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>5000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2718,7 +2835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2787,7 +2904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2845,7 +2962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2903,7 +3020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084E9BD6-5E43-44C7-A877-8C0A5F54A7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B4D53C-EBCC-46F0-8AE6-7EB48EDE51DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="13" activeTab="14" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1623,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" customWidth="1"/>
@@ -1653,17 +1653,6 @@
         <v>3651</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B4D53C-EBCC-46F0-8AE6-7EB48EDE51DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448D4A2C-A843-4A08-B0FF-EE793731D799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="33" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448D4A2C-A843-4A08-B0FF-EE793731D799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB854FF-03A4-48E4-BC30-5DFDE03D0E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="31" activeTab="33" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -1650,7 +1650,7 @@
         <v>77</v>
       </c>
       <c r="C2">
-        <v>3651</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB854FF-03A4-48E4-BC30-5DFDE03D0E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E732AF1-43CD-43B3-9D67-AD36E9637FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -1650,7 +1650,7 @@
         <v>77</v>
       </c>
       <c r="C2">
-        <v>70</v>
+        <v>3670</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E732AF1-43CD-43B3-9D67-AD36E9637FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B002707D-8F5E-4377-BDCC-87366B41EEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="19" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -33,26 +33,27 @@
     <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId18"/>
     <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId19"/>
     <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId20"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId21"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId22"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId23"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId24"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId25"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId26"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId27"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId28"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId29"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId30"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId31"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId32"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId33"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId34"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId35"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId36"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId37"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId38"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId39"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId40"/>
+    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId21"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId22"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId23"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId24"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId25"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId26"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId27"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId28"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId29"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId30"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId31"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId32"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId33"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId34"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId35"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId36"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId37"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId38"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId39"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId40"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId41"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1659,6 +1660,42 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66275926-57AE-411B-AAAD-10242088CD96}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.44140625" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2">
+        <v>3630</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1706,7 +1743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1754,7 +1791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1812,7 +1849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1859,7 +1896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1918,7 +1955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1988,7 +2025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2101,7 +2138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2240,53 +2277,6 @@
       </c>
       <c r="C12" t="s">
         <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
       </c>
     </row>
   </sheetData>
@@ -2364,6 +2354,53 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2454,7 +2491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2545,7 +2582,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2603,7 +2640,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2706,7 +2743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2754,7 +2791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2845,7 +2882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2948,7 +2985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3017,7 +3054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3068,64 +3105,6 @@
       </c>
       <c r="C4" t="s">
         <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3214,6 +3193,64 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75E1ECFE-F7C1-487F-B0B4-333116DBA707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B2F5FD-2806-42E3-9E9C-D6223A9F5794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="30" activeTab="32" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="13" activeTab="15" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -26,31 +26,33 @@
     <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId11"/>
     <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId12"/>
     <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId13"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId14"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId15"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId16"/>
-    <sheet name="Sheet1" sheetId="33" r:id="rId17"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId18"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId19"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId20"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId21"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId22"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId23"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId24"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId25"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId26"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId27"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId28"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId29"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId30"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId31"/>
-    <sheet name="Grantee_PRenewal_Creation" sheetId="38" r:id="rId32"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId33"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId34"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId35"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId36"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId37"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId38"/>
+    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId14"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId15"/>
+    <sheet name="Grantee_BPC_Edition" sheetId="41" r:id="rId16"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId17"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId18"/>
+    <sheet name="Sheet1" sheetId="33" r:id="rId19"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId20"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId21"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId22"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId23"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId24"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId25"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId26"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId27"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId28"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId29"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId30"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId31"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId32"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId33"/>
+    <sheet name="Grantee_PRenewal_Creation" sheetId="38" r:id="rId34"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId35"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId36"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId37"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId38"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId39"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1193,6 +1195,75 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B1B6EA-EC6D-4222-9617-65FD397509F9}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1251,7 +1322,54 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F036D49-E23C-439C-8128-14CC6E5917FD}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2">
+        <v>3651</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1320,7 +1438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1400,7 +1518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1409,7 +1527,76 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEC1918-8771-4526-A90D-55EE42978FB3}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1457,7 +1644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1505,13 +1692,177 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFEC1918-8771-4526-A90D-55EE42978FB3}">
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -1533,7 +1884,7 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1571,38 +1922,39 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1610,10 +1962,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1621,104 +1973,112 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>64</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1726,58 +2086,192 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1785,91 +2279,21 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
+      <c r="B5" t="s">
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1877,476 +2301,21 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
       <c r="B7" t="s">
         <v>61</v>
       </c>
       <c r="C7">
         <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2424,6 +2393,155 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2526,7 +2644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2617,7 +2735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D37BD41-3509-4274-A8BB-C767D9F8146D}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2686,7 +2804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6446ACD1-050C-4595-A324-AF366517EC90}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2732,7 +2850,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2835,7 +2953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2904,7 +3022,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2962,7 +3080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3013,97 +3131,6 @@
       </c>
       <c r="C4" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3191,6 +3218,97 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE5594E6-CDC4-4068-99A2-0F1E0C84230B}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58B2F5FD-2806-42E3-9E9C-D6223A9F5794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D954A01B-A096-45CF-8AE6-08F761DADC7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="13" activeTab="15" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1324,7 +1324,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F036D49-E23C-439C-8128-14CC6E5917FD}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
@@ -1351,17 +1351,6 @@
       </c>
       <c r="C2">
         <v>3651</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B002707D-8F5E-4377-BDCC-87366B41EEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFFFBBE-AA67-49CC-A20F-F3D6AE25ACD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="18" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -34,26 +34,27 @@
     <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId19"/>
     <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId20"/>
     <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId21"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId22"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId23"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId24"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId25"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId26"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId27"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId28"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId29"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId30"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId31"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId32"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId33"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId34"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId35"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId36"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId37"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId38"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId39"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId40"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId41"/>
+    <sheet name="Grantee_GrantCreationNonCashSub" sheetId="43" r:id="rId22"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId23"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId24"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId25"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId26"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId27"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId28"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId29"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId30"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId31"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId32"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId33"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId34"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId35"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId36"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId37"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId38"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId39"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId40"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId41"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId42"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="106">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -360,6 +361,39 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Automation Runtime Direct Award</t>
+  </si>
+  <si>
+    <t>GrantNumber__c</t>
+  </si>
+  <si>
+    <t>TotalObligatedAmount__c</t>
+  </si>
+  <si>
+    <t>GrantType__c</t>
+  </si>
+  <si>
+    <t>Project Grant</t>
+  </si>
+  <si>
+    <t>DoesGrantAllowIndirect__c</t>
+  </si>
+  <si>
+    <t>MaintenanceOfEffort__c</t>
+  </si>
+  <si>
+    <t>GranteeMatch__c</t>
+  </si>
+  <si>
+    <t>CostSharing__c</t>
+  </si>
+  <si>
+    <t>Cash and Non-Cash Match</t>
+  </si>
+  <si>
+    <t>Department of Education</t>
   </si>
 </sst>
 </file>
@@ -432,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -450,6 +484,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1696,6 +1733,208 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3867061B-5475-4BA0-A374-8CECDD9D9B11}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" customWidth="1"/>
+    <col min="3" max="3" width="30.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" s="9">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="9">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1743,7 +1982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1791,7 +2030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1849,7 +2088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1896,7 +2135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1955,7 +2194,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2025,7 +2264,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2131,152 +2370,6 @@
       </c>
       <c r="C9" t="s">
         <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2354,6 +2447,152 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2400,7 +2639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2491,7 +2730,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2582,7 +2821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2640,7 +2879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2743,7 +2982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2791,7 +3030,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2882,7 +3121,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2985,7 +3224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3046,64 +3285,6 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3193,6 +3374,64 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3250,7 +3489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFFFBBE-AA67-49CC-A20F-F3D6AE25ACD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1301170B-32CF-4E66-B72A-A725F281A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -34,27 +34,26 @@
     <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId19"/>
     <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId20"/>
     <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId21"/>
-    <sheet name="Grantee_GrantCreationNonCashSub" sheetId="43" r:id="rId22"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId23"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId24"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId25"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId26"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId27"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId28"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId29"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId30"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId31"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId32"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId33"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId34"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId35"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId36"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId37"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId38"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId39"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId40"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId41"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId42"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId22"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId23"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId24"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId25"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId26"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId27"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId28"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId29"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId30"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId31"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId32"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId33"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId34"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId35"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId36"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId37"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId38"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId39"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId40"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId41"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -361,39 +360,6 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>Automation Runtime Direct Award</t>
-  </si>
-  <si>
-    <t>GrantNumber__c</t>
-  </si>
-  <si>
-    <t>TotalObligatedAmount__c</t>
-  </si>
-  <si>
-    <t>GrantType__c</t>
-  </si>
-  <si>
-    <t>Project Grant</t>
-  </si>
-  <si>
-    <t>DoesGrantAllowIndirect__c</t>
-  </si>
-  <si>
-    <t>MaintenanceOfEffort__c</t>
-  </si>
-  <si>
-    <t>GranteeMatch__c</t>
-  </si>
-  <si>
-    <t>CostSharing__c</t>
-  </si>
-  <si>
-    <t>Cash and Non-Cash Match</t>
-  </si>
-  <si>
-    <t>Department of Education</t>
   </si>
 </sst>
 </file>
@@ -466,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -484,9 +450,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1733,208 +1696,6 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3867061B-5475-4BA0-A374-8CECDD9D9B11}">
-  <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="30.21875" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C4" s="9">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="9">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C8" s="9">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" s="9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1982,7 +1743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2030,7 +1791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2088,7 +1849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2135,7 +1896,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2194,7 +1955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2264,7 +2025,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2370,6 +2131,152 @@
       </c>
       <c r="C9" t="s">
         <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2447,45 +2354,92 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>52</v>
+      </c>
+      <c r="C3">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -2493,10 +2447,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -2504,10 +2458,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -2515,10 +2469,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -2526,447 +2480,254 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7">
+        <v>3650</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5">
+        <v>4017</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7">
-        <v>3650</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="5">
-        <v>4017</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="6" t="s">
@@ -2982,7 +2743,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3030,7 +2791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3121,7 +2882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3224,7 +2985,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3285,6 +3046,64 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3374,107 +3193,49 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
@@ -3489,7 +3250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1301170B-32CF-4E66-B72A-A725F281A47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA5C157-8469-4BFF-BC4E-749D021D64C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="21" activeTab="21" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="5760" yWindow="2688" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA5C157-8469-4BFF-BC4E-749D021D64C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE373089-6A08-4C62-99CA-38E9447CEC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5760" yWindow="2688" windowWidth="17280" windowHeight="8880" firstSheet="19" activeTab="20" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -21,39 +21,41 @@
     <sheet name="Budget_Redirection" sheetId="15" r:id="rId6"/>
     <sheet name="Grantee_Budget_Redirection" sheetId="36" r:id="rId7"/>
     <sheet name="Grantee_PRenewal_Creation" sheetId="38" r:id="rId8"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId9"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId10"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId11"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId12"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId13"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId14"/>
-    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId15"/>
-    <sheet name="Sheet3" sheetId="41" r:id="rId16"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId17"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId18"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId19"/>
-    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId20"/>
-    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId21"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId22"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId23"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId24"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId25"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId26"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId27"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId28"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId29"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId30"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId31"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId32"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId33"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId34"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId35"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId36"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId37"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId38"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId39"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId40"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId41"/>
+    <sheet name="Grantee_Other_Creation" sheetId="43" r:id="rId9"/>
+    <sheet name="Grantee_Other_Edition" sheetId="44" r:id="rId10"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId11"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId12"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId13"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId14"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId15"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId16"/>
+    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId17"/>
+    <sheet name="Sheet3" sheetId="41" r:id="rId18"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId19"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId20"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId21"/>
+    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId22"/>
+    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId23"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId24"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId25"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId26"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId27"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId28"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId29"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId30"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId31"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId32"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId33"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId34"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId35"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId36"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId37"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId38"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId39"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId40"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId41"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId42"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId43"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -75,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="100">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -360,6 +362,21 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>OtherChangeDescription__c</t>
+  </si>
+  <si>
+    <t>PurposeSummary__c</t>
+  </si>
+  <si>
+    <t>OtherAmendmentTypeDetails__c</t>
+  </si>
+  <si>
+    <t>Automation test</t>
   </si>
 </sst>
 </file>
@@ -822,6 +839,133 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE2E8D66-9322-498A-A789-5ABBEB9CB68E}">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.88671875" customWidth="1"/>
+    <col min="3" max="3" width="32.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -890,7 +1034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -948,7 +1092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1084,7 +1228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1209,7 +1353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1267,7 +1411,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A04F876-0CD3-4EAF-9941-AF87F65CFA3E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1336,7 +1480,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AD510-703D-495D-9F32-51DAD0BC6535}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1345,7 +1489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1401,155 +1545,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1623,6 +1618,155 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1659,7 +1803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66275926-57AE-411B-AAAD-10242088CD96}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1695,7 +1839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1743,7 +1887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1791,7 +1935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1849,7 +1993,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1896,7 +2040,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1955,7 +2099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2022,265 +2166,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5">
-        <v>3650</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2354,6 +2239,265 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="29.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2400,7 +2544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2491,7 +2635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2582,7 +2726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2640,7 +2784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2743,7 +2887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2791,7 +2935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2882,7 +3026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2985,133 +3129,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
   <dimension ref="A1:C6"/>
@@ -3193,6 +3210,133 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3250,7 +3394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3605,12 +3749,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC7AEDF-468A-484A-BE9D-9B9919098319}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -3628,22 +3772,22 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>86</v>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3657,8 +3801,18 @@
         <v>6</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE373089-6A08-4C62-99CA-38E9447CEC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA4F2E9-845C-4A00-BCAA-B5FBF850CBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="8" activeTab="9" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -23,39 +23,41 @@
     <sheet name="Grantee_PRenewal_Creation" sheetId="38" r:id="rId8"/>
     <sheet name="Grantee_Other_Creation" sheetId="43" r:id="rId9"/>
     <sheet name="Grantee_Other_Edition" sheetId="44" r:id="rId10"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId11"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId12"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId13"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId14"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId15"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId16"/>
-    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId17"/>
-    <sheet name="Sheet3" sheetId="41" r:id="rId18"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId19"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId20"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId21"/>
-    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId22"/>
-    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId23"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId24"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId25"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId26"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId27"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId28"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId29"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId30"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId31"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId32"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId33"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId34"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId35"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId36"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId37"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId38"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId39"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId40"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId41"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId42"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId43"/>
+    <sheet name="Grantee_Combination_Creation" sheetId="45" r:id="rId11"/>
+    <sheet name="Grantee_Combination_Edition" sheetId="46" r:id="rId12"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId13"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId14"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId15"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId16"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId17"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId18"/>
+    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId19"/>
+    <sheet name="Sheet3" sheetId="41" r:id="rId20"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId21"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId22"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId23"/>
+    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId24"/>
+    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId25"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId26"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId27"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId28"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId29"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId30"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId31"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId32"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId33"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId34"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId35"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId36"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId37"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId38"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId39"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId40"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId41"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId42"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId43"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId44"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId45"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="100">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -907,6 +909,173 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3F84230-0190-4A53-A50E-1EC920CF7F1B}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.5546875" customWidth="1"/>
+    <col min="3" max="3" width="25.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10BC853C-E59D-462C-832F-DBE3D9728CED}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -965,7 +1134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1034,7 +1203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1092,7 +1261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1228,7 +1397,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1353,7 +1522,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1411,7 +1580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A04F876-0CD3-4EAF-9941-AF87F65CFA3E}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1477,74 +1646,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AD510-703D-495D-9F32-51DAD0BC6535}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1618,6 +1719,74 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AD510-703D-495D-9F32-51DAD0BC6535}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1686,7 +1855,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1766,7 +1935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1803,7 +1972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66275926-57AE-411B-AAAD-10242088CD96}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1839,7 +2008,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1887,7 +2056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1935,7 +2104,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1993,7 +2162,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2037,135 +2206,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="28.21875" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2239,6 +2279,135 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7F1F928-5062-4480-A5CB-C00A65CDBE7D}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C815A42-528B-459D-841C-D44FE9FA6020}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="28.21875" customWidth="1"/>
+    <col min="3" max="3" width="48.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51772752-268C-420F-8F6C-3EB44DC586C7}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2351,7 +2520,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D1BAA82-C6A0-43F4-ACD7-0F51FAC17BDE}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2497,7 +2666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B98C2E6-0C38-44BD-BCCA-D74A75F16055}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2544,7 +2713,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36CE4AB1-D2A4-48AD-BE1D-510D3EC12A32}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2635,7 +2804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6AF52C3-BB99-4CC4-A56A-57677D233764}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2726,7 +2895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF2024B-3855-4F21-818F-72BDEF018EB6}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2784,7 +2953,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6731B0-0A3A-4C99-9219-CD51FBCA919D}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2887,7 +3056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD74361-B805-43B7-866E-3D05313584E4}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2935,7 +3104,87 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B83EB6-336A-474A-9B4D-6ACB3B6F82BD}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3026,7 +3275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553CC38A-2DBF-46D2-8E76-C45CC7EF93DF}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3129,9 +3378,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD4347D0-7C7B-4991-B39A-D56700E62FF3}">
-  <dimension ref="A1:C6"/>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -3157,7 +3406,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3168,7 +3417,7 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3176,10 +3425,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -3187,35 +3436,24 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62770C67-3364-43CF-8FC9-172E7743FC1C}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -3237,7 +3475,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -3245,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -3256,130 +3494,61 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F7F05-2D11-4E6A-A090-87D63AD5B8AF}">
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
+    <col min="2" max="2" width="34.44140625" customWidth="1"/>
+    <col min="3" max="3" width="28.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D7310-4879-4774-96F6-2BF800BB522F}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="34.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
@@ -3394,7 +3563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DFDBA76-585A-4956-AF61-28921A0073B1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEA4F2E9-845C-4A00-BCAA-B5FBF850CBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB2C3C6-DD0F-46EA-B979-F892E371843F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
   <sheets>
     <sheet name="ScopeOfWork_Creation" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="100">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1023,8 +1023,12 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10BC853C-E59D-462C-832F-DBE3D9728CED}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.33203125" customWidth="1"/>
+    <col min="3" max="3" width="29.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -1041,22 +1045,22 @@
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2">
+        <v>3670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -1064,9 +1068,20 @@
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C5" t="s">
         <v>99</v>
       </c>
     </row>

--- a/src/main/resources/AmendmentRequest_Field_Values.xlsx
+++ b/src/main/resources/AmendmentRequest_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DB2C3C6-DD0F-46EA-B979-F892E371843F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FBC820-F32D-4B92-9462-7023854CE3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="11" xr2:uid="{371138BB-CE66-4BB7-8C3C-9638AA0A141A}"/>
   </bookViews>
@@ -24,40 +24,41 @@
     <sheet name="Grantee_Other_Creation" sheetId="43" r:id="rId9"/>
     <sheet name="Grantee_Other_Edition" sheetId="44" r:id="rId10"/>
     <sheet name="Grantee_Combination_Creation" sheetId="45" r:id="rId11"/>
-    <sheet name="Grantee_Combination_Edition" sheetId="46" r:id="rId12"/>
-    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId13"/>
-    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId14"/>
-    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId15"/>
-    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId16"/>
-    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId17"/>
-    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId18"/>
-    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId19"/>
-    <sheet name="Sheet3" sheetId="41" r:id="rId20"/>
-    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId21"/>
-    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId22"/>
-    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId23"/>
-    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId24"/>
-    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId25"/>
-    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId26"/>
-    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId27"/>
-    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId28"/>
-    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId29"/>
-    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId30"/>
-    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId31"/>
-    <sheet name="GrantCreation" sheetId="6" r:id="rId32"/>
-    <sheet name="GrantEdition" sheetId="7" r:id="rId33"/>
-    <sheet name="Edition_Standalone" sheetId="8" r:id="rId34"/>
-    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId35"/>
-    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId36"/>
-    <sheet name="Periodic Renewal" sheetId="12" r:id="rId37"/>
-    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId38"/>
-    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId39"/>
-    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId40"/>
-    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId41"/>
-    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId42"/>
-    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId43"/>
-    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId44"/>
-    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId45"/>
+    <sheet name="Grantee_Combination_Creation2" sheetId="47" r:id="rId12"/>
+    <sheet name="Grantee_Combination_Edition" sheetId="46" r:id="rId13"/>
+    <sheet name="Subrecipient_BRedirection" sheetId="21" r:id="rId14"/>
+    <sheet name="Subrecipient_BRedirec_Carry_Err" sheetId="29" r:id="rId15"/>
+    <sheet name="Subrecipient_KPC" sheetId="22" r:id="rId16"/>
+    <sheet name="ScopeOfWork_Edition" sheetId="2" r:id="rId17"/>
+    <sheet name="Subrecipient_SOW_Edition" sheetId="18" r:id="rId18"/>
+    <sheet name="BudgetPeriodChange_Creation" sheetId="3" r:id="rId19"/>
+    <sheet name="Grantee_BPC_Creation" sheetId="40" r:id="rId20"/>
+    <sheet name="Sheet3" sheetId="41" r:id="rId21"/>
+    <sheet name="SubRecipientBPC_Creation" sheetId="19" r:id="rId22"/>
+    <sheet name="Subrecipient_BPCSOW_Creation" sheetId="26" r:id="rId23"/>
+    <sheet name="Sub_BR_KPC_SOW_creation" sheetId="31" r:id="rId24"/>
+    <sheet name="Grantee_BPC_Edition" sheetId="33" r:id="rId25"/>
+    <sheet name="Grantee_BPC_Edition2" sheetId="42" r:id="rId26"/>
+    <sheet name="BudgetPeriodChange_Edition" sheetId="4" r:id="rId27"/>
+    <sheet name="SubRecipientBPC_Edition" sheetId="20" r:id="rId28"/>
+    <sheet name="SubRecipientCF_Creation" sheetId="23" r:id="rId29"/>
+    <sheet name="PaymentRequestEdition" sheetId="11" r:id="rId30"/>
+    <sheet name="FundingChange_Creation" sheetId="5" r:id="rId31"/>
+    <sheet name="Grantee_FundingChange_Creation" sheetId="35" r:id="rId32"/>
+    <sheet name="GrantCreation" sheetId="6" r:id="rId33"/>
+    <sheet name="GrantEdition" sheetId="7" r:id="rId34"/>
+    <sheet name="Edition_Standalone" sheetId="8" r:id="rId35"/>
+    <sheet name="Payment Request Schedule" sheetId="9" r:id="rId36"/>
+    <sheet name="Progress Report Schedule" sheetId="10" r:id="rId37"/>
+    <sheet name="Periodic Renewal" sheetId="12" r:id="rId38"/>
+    <sheet name="Periodic Renewal Edition" sheetId="13" r:id="rId39"/>
+    <sheet name="Grantee_PeriodicRenewal_Edition" sheetId="39" r:id="rId40"/>
+    <sheet name="PeriodicEditionFocusYes" sheetId="32" r:id="rId41"/>
+    <sheet name="Periodic Renewal Edition1" sheetId="28" r:id="rId42"/>
+    <sheet name="Funding_Terms_creation" sheetId="24" r:id="rId43"/>
+    <sheet name="TermsAndConditions_Creation" sheetId="14" r:id="rId44"/>
+    <sheet name="Subrecipient_BD_KP_SOW_Edition" sheetId="34" r:id="rId45"/>
+    <sheet name="AllAmendment_Creation" sheetId="27" r:id="rId46"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -79,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="100">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1022,6 +1023,119 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E689B53-7506-46E2-93BA-8A633A0D36FF}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10BC853C-E59D-462C-832F-DBE3D9728CED}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1090,7 +1204,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1C7C3E9-7A91-479E-8DB7-C5289494DF22}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1149,7 +1263,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA7DC5-C4A1-4E9C-B02D-9945A615B758}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1218,7 +1332,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F956442-5D32-41A9-9373-4CEFD36ACD4B}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1276,7 +1390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF3C3D45-7E71-472A-AB14-3D5373D782BA}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1412,7 +1526,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B2B8548-7B25-4129-9EB7-BF1BA0DF00C4}">
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1537,7 +1651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF0DD9D3-0F99-4CAD-B5E8-028A0FF50760}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1587,75 +1701,6 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A04F876-0CD3-4EAF-9941-AF87F65CFA3E}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1734,6 +1779,75 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A04F876-0CD3-4EAF-9941-AF87F65CFA3E}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{662AD510-703D-495D-9F32-51DAD0BC6535}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1742,7 +1856,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25797962-2CD8-4222-8F0C-F2737F68CB74}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1801,7 +1915,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EBA5DFF-498D-4D83-B948-A4DE3D93557A}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1870,7 +1984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7391CE8D-3E64-4DF2-B815-01A045EEFFCE}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1950,7 +2064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F90B4C34-DF4F-458F-B7E9-57B6FA94EB25}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1987,7 +2101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66275926-57AE-411B-AAAD-10242088CD96}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2023,7 +2137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AF2254-AE3B-4E5C-85F3-E6BD713DEDBA}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2071,7 +2185,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F116B932-6CC5-49E6-907B-B1FB48B4CADD}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2119,7 +2233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB9B001-FDE9-4CB7-8749-6B43410AD625}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2170,53 +2284,6 @@
       </c>
       <c r="C4" t="s">
         <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2294,6 +2361,53 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5E7F2A7-80D1-499C-A4FA-A74EFAC3E1B6}">
+  <dimension ref="A1:C